--- a/data/proteomics/membrane_size_across_compartment_jianye_C_limitation.xlsx
+++ b/data/proteomics/membrane_size_across_compartment_jianye_C_limitation.xlsx
@@ -490,31 +490,31 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>471.6101245238627</v>
+        <v>471.610124523862</v>
       </c>
       <c r="D2" t="n">
-        <v>484.1043791799472</v>
+        <v>484.1043791799478</v>
       </c>
       <c r="E2" t="n">
-        <v>493.069482002543</v>
+        <v>493.0694820025428</v>
       </c>
       <c r="F2" t="n">
-        <v>518.4759260461843</v>
+        <v>518.4759260461844</v>
       </c>
       <c r="G2" t="n">
-        <v>368.3969197341384</v>
+        <v>368.3969197341382</v>
       </c>
       <c r="H2" t="n">
-        <v>415.4885168203948</v>
+        <v>415.4885168203949</v>
       </c>
       <c r="I2" t="n">
-        <v>423.3473965008862</v>
+        <v>423.3473965008861</v>
       </c>
       <c r="J2" t="n">
-        <v>406.3637823558904</v>
+        <v>406.3637823558906</v>
       </c>
       <c r="K2" t="n">
-        <v>348.1218417523614</v>
+        <v>348.1218417523612</v>
       </c>
     </row>
     <row r="3">
@@ -533,16 +533,16 @@
         <v>0.8073556894374631</v>
       </c>
       <c r="E3" t="n">
-        <v>0.8830444809977521</v>
+        <v>0.883044480997752</v>
       </c>
       <c r="F3" t="n">
         <v>0.9730140640652736</v>
       </c>
       <c r="G3" t="n">
-        <v>0.6998438852556166</v>
+        <v>0.6998438852556168</v>
       </c>
       <c r="H3" t="n">
-        <v>0.7677084225954881</v>
+        <v>0.767708422595488</v>
       </c>
       <c r="I3" t="n">
         <v>0.7639155170086435</v>
@@ -567,7 +567,7 @@
         <v>1.099698308066571</v>
       </c>
       <c r="D4" t="n">
-        <v>1.149497887552204</v>
+        <v>1.149497887552203</v>
       </c>
       <c r="E4" t="n">
         <v>1.361541114483235</v>
@@ -641,28 +641,28 @@
         <v>279.7630509703158</v>
       </c>
       <c r="D6" t="n">
-        <v>275.0156570537724</v>
+        <v>275.0156570537727</v>
       </c>
       <c r="E6" t="n">
         <v>264.8151799075945</v>
       </c>
       <c r="F6" t="n">
-        <v>268.3651820730988</v>
+        <v>268.365182073099</v>
       </c>
       <c r="G6" t="n">
         <v>183.1214182173784</v>
       </c>
       <c r="H6" t="n">
-        <v>198.9552126813234</v>
+        <v>198.9552126813232</v>
       </c>
       <c r="I6" t="n">
-        <v>203.2858258267507</v>
+        <v>203.2858258267506</v>
       </c>
       <c r="J6" t="n">
-        <v>208.3458363097292</v>
+        <v>208.3458363097289</v>
       </c>
       <c r="K6" t="n">
-        <v>190.0815168751498</v>
+        <v>190.08151687515</v>
       </c>
     </row>
     <row r="7">
@@ -675,31 +675,31 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>596.5033628407524</v>
+        <v>596.5033628407523</v>
       </c>
       <c r="D7" t="n">
-        <v>602.1532518076874</v>
+        <v>602.153251807687</v>
       </c>
       <c r="E7" t="n">
-        <v>633.0102502599491</v>
+        <v>633.0102502599492</v>
       </c>
       <c r="F7" t="n">
-        <v>682.2499829917829</v>
+        <v>682.2499829917837</v>
       </c>
       <c r="G7" t="n">
-        <v>495.0102083876344</v>
+        <v>495.0102083876342</v>
       </c>
       <c r="H7" t="n">
-        <v>569.251529878032</v>
+        <v>569.2515298780327</v>
       </c>
       <c r="I7" t="n">
-        <v>588.2343187633131</v>
+        <v>588.2343187633141</v>
       </c>
       <c r="J7" t="n">
-        <v>615.6162777202662</v>
+        <v>615.6162777202668</v>
       </c>
       <c r="K7" t="n">
-        <v>565.0920009981148</v>
+        <v>565.0920009981153</v>
       </c>
     </row>
     <row r="8">
@@ -712,31 +712,31 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>273.8337956832382</v>
+        <v>273.8337956832381</v>
       </c>
       <c r="D8" t="n">
-        <v>281.7892126955921</v>
+        <v>281.789212695592</v>
       </c>
       <c r="E8" t="n">
-        <v>274.2530049535598</v>
+        <v>274.2530049535596</v>
       </c>
       <c r="F8" t="n">
-        <v>281.3470738387155</v>
+        <v>281.3470738387154</v>
       </c>
       <c r="G8" t="n">
-        <v>190.4859590569804</v>
+        <v>190.4859590569803</v>
       </c>
       <c r="H8" t="n">
-        <v>207.3712166243198</v>
+        <v>207.3712166243199</v>
       </c>
       <c r="I8" t="n">
-        <v>218.3175964949519</v>
+        <v>218.3175964949517</v>
       </c>
       <c r="J8" t="n">
-        <v>217.2490533174909</v>
+        <v>217.2490533174911</v>
       </c>
       <c r="K8" t="n">
-        <v>194.1195221250503</v>
+        <v>194.1195221250504</v>
       </c>
     </row>
     <row r="9">
@@ -749,7 +749,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>46.64004514159267</v>
+        <v>46.64004514159268</v>
       </c>
       <c r="D9" t="n">
         <v>47.04582068687336</v>
@@ -758,22 +758,22 @@
         <v>43.04217974741861</v>
       </c>
       <c r="F9" t="n">
-        <v>44.3193742300133</v>
+        <v>44.31937423001332</v>
       </c>
       <c r="G9" t="n">
-        <v>31.09077871273075</v>
+        <v>31.09077871273074</v>
       </c>
       <c r="H9" t="n">
         <v>33.70071191492654</v>
       </c>
       <c r="I9" t="n">
-        <v>35.14010477226744</v>
+        <v>35.14010477226743</v>
       </c>
       <c r="J9" t="n">
-        <v>36.50687992398388</v>
+        <v>36.50687992398387</v>
       </c>
       <c r="K9" t="n">
-        <v>32.12833548186901</v>
+        <v>32.12833548186902</v>
       </c>
     </row>
     <row r="10">
@@ -823,13 +823,13 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>68.81184725728684</v>
+        <v>68.81184725728683</v>
       </c>
       <c r="D11" t="n">
         <v>68.50994206581662</v>
       </c>
       <c r="E11" t="n">
-        <v>55.27478084380221</v>
+        <v>55.27478084380222</v>
       </c>
       <c r="F11" t="n">
         <v>51.20329747291028</v>
@@ -844,7 +844,7 @@
         <v>31.27415114794129</v>
       </c>
       <c r="J11" t="n">
-        <v>32.13257933344176</v>
+        <v>32.13257933344177</v>
       </c>
       <c r="K11" t="n">
         <v>27.66221845340653</v>
@@ -860,22 +860,22 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>26.4344108302075</v>
+        <v>26.43441083020748</v>
       </c>
       <c r="D12" t="n">
-        <v>28.65214804087489</v>
+        <v>28.6521480408749</v>
       </c>
       <c r="E12" t="n">
-        <v>34.96801094320348</v>
+        <v>34.9680109432035</v>
       </c>
       <c r="F12" t="n">
-        <v>36.65814969823049</v>
+        <v>36.65814969823048</v>
       </c>
       <c r="G12" t="n">
-        <v>24.53865865154333</v>
+        <v>24.53865865154334</v>
       </c>
       <c r="H12" t="n">
-        <v>24.59674733099058</v>
+        <v>24.5967473309906</v>
       </c>
       <c r="I12" t="n">
         <v>22.71504284267651</v>
@@ -884,7 +884,7 @@
         <v>21.75834333565711</v>
       </c>
       <c r="K12" t="n">
-        <v>19.38952515565516</v>
+        <v>19.38952515565517</v>
       </c>
     </row>
     <row r="13">
@@ -897,7 +897,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.879581566419496</v>
+        <v>0.8795815664194963</v>
       </c>
       <c r="D13" t="n">
         <v>1.049940423215425</v>
@@ -909,16 +909,16 @@
         <v>1.703291567016635</v>
       </c>
       <c r="G13" t="n">
-        <v>1.311251367817391</v>
+        <v>1.31125136781739</v>
       </c>
       <c r="H13" t="n">
-        <v>1.500071324782904</v>
+        <v>1.500071324782905</v>
       </c>
       <c r="I13" t="n">
         <v>1.383592379527649</v>
       </c>
       <c r="J13" t="n">
-        <v>1.29192019873448</v>
+        <v>1.291920198734479</v>
       </c>
       <c r="K13" t="n">
         <v>1.17780622391137</v>
@@ -934,19 +934,19 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>26.95108104831671</v>
+        <v>26.9510810483167</v>
       </c>
       <c r="D14" t="n">
         <v>28.31909718602468</v>
       </c>
       <c r="E14" t="n">
-        <v>30.62587428960055</v>
+        <v>30.62587428960054</v>
       </c>
       <c r="F14" t="n">
         <v>31.31964628727424</v>
       </c>
       <c r="G14" t="n">
-        <v>21.67669867716534</v>
+        <v>21.67669867716533</v>
       </c>
       <c r="H14" t="n">
         <v>22.45006461569978</v>
@@ -955,7 +955,7 @@
         <v>20.72304828050982</v>
       </c>
       <c r="J14" t="n">
-        <v>19.00807382848332</v>
+        <v>19.00807382848331</v>
       </c>
       <c r="K14" t="n">
         <v>15.58913322993365</v>
@@ -983,7 +983,7 @@
         <v>11.99930851024916</v>
       </c>
       <c r="G15" t="n">
-        <v>8.58275230594433</v>
+        <v>8.582752305944329</v>
       </c>
       <c r="H15" t="n">
         <v>9.233220464201233</v>
@@ -995,7 +995,7 @@
         <v>9.053910611694908</v>
       </c>
       <c r="K15" t="n">
-        <v>6.799284378290424</v>
+        <v>6.799284378290425</v>
       </c>
     </row>
     <row r="16">
@@ -1008,7 +1008,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>2.823957844585715</v>
+        <v>2.823957844585716</v>
       </c>
       <c r="D16" t="n">
         <v>2.907202563424667</v>
@@ -1032,7 +1032,7 @@
         <v>3.409373418927582</v>
       </c>
       <c r="K16" t="n">
-        <v>3.003341383973697</v>
+        <v>3.003341383973696</v>
       </c>
     </row>
     <row r="17">
@@ -1048,13 +1048,13 @@
         <v>5.774156681466004</v>
       </c>
       <c r="D17" t="n">
-        <v>5.297221230916648</v>
+        <v>5.297221230916649</v>
       </c>
       <c r="E17" t="n">
-        <v>3.996275033158124</v>
+        <v>3.996275033158125</v>
       </c>
       <c r="F17" t="n">
-        <v>3.3349178076284</v>
+        <v>3.334917807628399</v>
       </c>
       <c r="G17" t="n">
         <v>1.639568578447067</v>
@@ -1066,7 +1066,7 @@
         <v>1.617666222126311</v>
       </c>
       <c r="J17" t="n">
-        <v>1.496887298944731</v>
+        <v>1.496887298944732</v>
       </c>
       <c r="K17" t="n">
         <v>1.376417282590316</v>
@@ -1085,25 +1085,25 @@
         <v>5.279636068497975</v>
       </c>
       <c r="D18" t="n">
-        <v>5.199944046805538</v>
+        <v>5.199944046805537</v>
       </c>
       <c r="E18" t="n">
         <v>5.913026887911635</v>
       </c>
       <c r="F18" t="n">
-        <v>6.311419255827178</v>
+        <v>6.311419255827179</v>
       </c>
       <c r="G18" t="n">
-        <v>4.616550100835493</v>
+        <v>4.616550100835491</v>
       </c>
       <c r="H18" t="n">
-        <v>5.058340164941544</v>
+        <v>5.058340164941547</v>
       </c>
       <c r="I18" t="n">
-        <v>4.839290956883596</v>
+        <v>4.839290956883594</v>
       </c>
       <c r="J18" t="n">
-        <v>4.944828056615342</v>
+        <v>4.944828056615341</v>
       </c>
       <c r="K18" t="n">
         <v>4.342472631377423</v>
@@ -1119,31 +1119,31 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>5.864882280077921</v>
+        <v>5.864882280077922</v>
       </c>
       <c r="D19" t="n">
-        <v>5.775152307999161</v>
+        <v>5.77515230799916</v>
       </c>
       <c r="E19" t="n">
-        <v>6.900959454646205</v>
+        <v>6.900959454646204</v>
       </c>
       <c r="F19" t="n">
         <v>7.441431138663534</v>
       </c>
       <c r="G19" t="n">
-        <v>5.607580413806615</v>
+        <v>5.607580413806613</v>
       </c>
       <c r="H19" t="n">
-        <v>6.181683247173207</v>
+        <v>6.181683247173208</v>
       </c>
       <c r="I19" t="n">
-        <v>6.053011677501911</v>
+        <v>6.053011677501908</v>
       </c>
       <c r="J19" t="n">
-        <v>5.925173492256197</v>
+        <v>5.925173492256195</v>
       </c>
       <c r="K19" t="n">
-        <v>5.135328266705728</v>
+        <v>5.135328266705725</v>
       </c>
     </row>
     <row r="20">
@@ -1162,7 +1162,7 @@
         <v>12.17770383403862</v>
       </c>
       <c r="E20" t="n">
-        <v>14.188724918397</v>
+        <v>14.18872491839699</v>
       </c>
       <c r="F20" t="n">
         <v>15.78631480588425</v>
@@ -1174,7 +1174,7 @@
         <v>13.15207666087779</v>
       </c>
       <c r="I20" t="n">
-        <v>13.56547735521572</v>
+        <v>13.56547735521573</v>
       </c>
       <c r="J20" t="n">
         <v>14.39506531535872</v>
@@ -1230,7 +1230,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>1.722862779369657</v>
+        <v>1.722862779369658</v>
       </c>
       <c r="D22" t="n">
         <v>1.658587585777259</v>
@@ -1248,7 +1248,7 @@
         <v>1.739956700967001</v>
       </c>
       <c r="I22" t="n">
-        <v>1.728807374488352</v>
+        <v>1.728807374488353</v>
       </c>
       <c r="J22" t="n">
         <v>1.621483664086336</v>
@@ -1270,7 +1270,7 @@
         <v>41.12110928632737</v>
       </c>
       <c r="D23" t="n">
-        <v>43.41595170736516</v>
+        <v>43.41595170736514</v>
       </c>
       <c r="E23" t="n">
         <v>39.87268743258092</v>
@@ -1304,7 +1304,7 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.06000357257826527</v>
+        <v>0.06000357257826528</v>
       </c>
       <c r="D24" t="n">
         <v>0.0677456156430789</v>
@@ -1322,13 +1322,13 @@
         <v>0.1045795887747484</v>
       </c>
       <c r="I24" t="n">
-        <v>0.06839260601778681</v>
+        <v>0.06839260601778682</v>
       </c>
       <c r="J24" t="n">
         <v>0.07024770638034204</v>
       </c>
       <c r="K24" t="n">
-        <v>0.05882677936999493</v>
+        <v>0.05882677936999494</v>
       </c>
     </row>
     <row r="25">
@@ -1344,13 +1344,13 @@
         <v>4.894108102346512</v>
       </c>
       <c r="D25" t="n">
-        <v>4.856093147160256</v>
+        <v>4.856093147160258</v>
       </c>
       <c r="E25" t="n">
-        <v>5.383138093669682</v>
+        <v>5.383138093669681</v>
       </c>
       <c r="F25" t="n">
-        <v>5.624771254482821</v>
+        <v>5.62477125448282</v>
       </c>
       <c r="G25" t="n">
         <v>4.121182743962621</v>
@@ -1359,13 +1359,13 @@
         <v>4.385791098378935</v>
       </c>
       <c r="I25" t="n">
-        <v>4.546454476565537</v>
+        <v>4.546454476565538</v>
       </c>
       <c r="J25" t="n">
-        <v>4.731030177396586</v>
+        <v>4.731030177396587</v>
       </c>
       <c r="K25" t="n">
-        <v>4.318769601793905</v>
+        <v>4.318769601793906</v>
       </c>
     </row>
     <row r="26">
@@ -1399,7 +1399,7 @@
         <v>1.817202747838853</v>
       </c>
       <c r="J26" t="n">
-        <v>1.739095060455207</v>
+        <v>1.739095060455208</v>
       </c>
       <c r="K26" t="n">
         <v>1.548962562830232</v>
@@ -1421,22 +1421,22 @@
         <v>20.92248238909474</v>
       </c>
       <c r="E27" t="n">
-        <v>27.1814677648802</v>
+        <v>27.18146776488019</v>
       </c>
       <c r="F27" t="n">
-        <v>31.98761512383236</v>
+        <v>31.98761512383235</v>
       </c>
       <c r="G27" t="n">
         <v>25.93485812578228</v>
       </c>
       <c r="H27" t="n">
-        <v>31.0936864765294</v>
+        <v>31.09368647652942</v>
       </c>
       <c r="I27" t="n">
-        <v>33.0104252808859</v>
+        <v>33.01042528088588</v>
       </c>
       <c r="J27" t="n">
-        <v>35.38217283926527</v>
+        <v>35.38217283926528</v>
       </c>
       <c r="K27" t="n">
         <v>33.38306303100899</v>
@@ -1452,16 +1452,16 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0.6506725100305512</v>
+        <v>0.650672510030551</v>
       </c>
       <c r="D28" t="n">
-        <v>0.6315108483847504</v>
+        <v>0.6315108483847505</v>
       </c>
       <c r="E28" t="n">
         <v>0.7117726684118162</v>
       </c>
       <c r="F28" t="n">
-        <v>0.7661336873714378</v>
+        <v>0.7661336873714379</v>
       </c>
       <c r="G28" t="n">
         <v>0.5857211179597976</v>
@@ -1470,10 +1470,10 @@
         <v>0.6649895533933434</v>
       </c>
       <c r="I28" t="n">
-        <v>0.6589575717023408</v>
+        <v>0.6589575717023407</v>
       </c>
       <c r="J28" t="n">
-        <v>0.6607092094790017</v>
+        <v>0.6607092094790018</v>
       </c>
       <c r="K28" t="n">
         <v>0.5727552590840561</v>
@@ -1585,28 +1585,28 @@
         <v>76.29508262274618</v>
       </c>
       <c r="D32" t="n">
-        <v>74.25425720587069</v>
+        <v>74.25425720587072</v>
       </c>
       <c r="E32" t="n">
         <v>71.82640449434564</v>
       </c>
       <c r="F32" t="n">
-        <v>74.07808872293083</v>
+        <v>74.07808872293086</v>
       </c>
       <c r="G32" t="n">
         <v>52.44079461960492</v>
       </c>
       <c r="H32" t="n">
-        <v>60.93574044827073</v>
+        <v>60.93574044827072</v>
       </c>
       <c r="I32" t="n">
-        <v>66.27328281608959</v>
+        <v>66.27328281608958</v>
       </c>
       <c r="J32" t="n">
-        <v>71.04686748179428</v>
+        <v>71.04686748179432</v>
       </c>
       <c r="K32" t="n">
-        <v>65.52274617106356</v>
+        <v>65.52274617106357</v>
       </c>
     </row>
     <row r="33">
@@ -1622,7 +1622,7 @@
         <v>31.62592342396609</v>
       </c>
       <c r="D33" t="n">
-        <v>32.93759695330079</v>
+        <v>32.9375969533008</v>
       </c>
       <c r="E33" t="n">
         <v>30.01337061924494</v>
@@ -1643,7 +1643,7 @@
         <v>23.17046439097195</v>
       </c>
       <c r="K33" t="n">
-        <v>19.74232548542231</v>
+        <v>19.7423254854223</v>
       </c>
     </row>
     <row r="34">
@@ -1674,10 +1674,10 @@
         <v>3.057790254991128</v>
       </c>
       <c r="I34" t="n">
-        <v>3.077464453182687</v>
+        <v>3.077464453182688</v>
       </c>
       <c r="J34" t="n">
-        <v>2.967361907703287</v>
+        <v>2.967361907703288</v>
       </c>
       <c r="K34" t="n">
         <v>2.58328165187708</v>
@@ -1711,10 +1711,10 @@
         <v>0.9645779621437065</v>
       </c>
       <c r="I35" t="n">
-        <v>0.9719955507124359</v>
+        <v>0.9719955507124358</v>
       </c>
       <c r="J35" t="n">
-        <v>0.8948321929765908</v>
+        <v>0.8948321929765909</v>
       </c>
       <c r="K35" t="n">
         <v>0.7628199718998454</v>
@@ -1730,7 +1730,7 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>1.607287015183337</v>
+        <v>1.607287015183338</v>
       </c>
       <c r="D36" t="n">
         <v>1.685192902556292</v>
@@ -1773,7 +1773,7 @@
         <v>22.01416567075024</v>
       </c>
       <c r="E37" t="n">
-        <v>26.76259419234142</v>
+        <v>26.7625941923414</v>
       </c>
       <c r="F37" t="n">
         <v>31.08724355173951</v>
@@ -1782,10 +1782,10 @@
         <v>25.67870644595383</v>
       </c>
       <c r="H37" t="n">
-        <v>31.10856921017296</v>
+        <v>31.10856921017295</v>
       </c>
       <c r="I37" t="n">
-        <v>35.60715899648194</v>
+        <v>35.60715899648193</v>
       </c>
       <c r="J37" t="n">
         <v>34.8515086087034</v>
@@ -1804,31 +1804,31 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>0.9738150782761174</v>
+        <v>0.9738150782761175</v>
       </c>
       <c r="D38" t="n">
-        <v>0.950987710745844</v>
+        <v>0.9509877107458439</v>
       </c>
       <c r="E38" t="n">
-        <v>0.9910038389929487</v>
+        <v>0.9910038389929486</v>
       </c>
       <c r="F38" t="n">
         <v>1.054976452710904</v>
       </c>
       <c r="G38" t="n">
-        <v>0.8224460034677638</v>
+        <v>0.8224460034677635</v>
       </c>
       <c r="H38" t="n">
-        <v>0.8998591926814044</v>
+        <v>0.8998591926814041</v>
       </c>
       <c r="I38" t="n">
-        <v>0.9234051614356404</v>
+        <v>0.9234051614356406</v>
       </c>
       <c r="J38" t="n">
         <v>0.8746249137611576</v>
       </c>
       <c r="K38" t="n">
-        <v>0.8035451524145992</v>
+        <v>0.803545152414599</v>
       </c>
     </row>
     <row r="39">
@@ -1853,10 +1853,10 @@
         <v>0.5795816487912481</v>
       </c>
       <c r="G39" t="n">
-        <v>0.441500170363589</v>
+        <v>0.4415001703635891</v>
       </c>
       <c r="H39" t="n">
-        <v>0.4580259425871504</v>
+        <v>0.4580259425871503</v>
       </c>
       <c r="I39" t="n">
         <v>0.4281679436946048</v>
@@ -1902,7 +1902,7 @@
         <v>0.4247241335149581</v>
       </c>
       <c r="K40" t="n">
-        <v>0.3888607693229225</v>
+        <v>0.3888607693229224</v>
       </c>
     </row>
     <row r="41">
@@ -1921,10 +1921,10 @@
         <v>1.469557266911898</v>
       </c>
       <c r="E41" t="n">
-        <v>1.740173635904137</v>
+        <v>1.740173635904136</v>
       </c>
       <c r="F41" t="n">
-        <v>1.919681619953622</v>
+        <v>1.919681619953621</v>
       </c>
       <c r="G41" t="n">
         <v>1.414961202304479</v>
@@ -1939,7 +1939,7 @@
         <v>1.640147068797114</v>
       </c>
       <c r="K41" t="n">
-        <v>1.522564454332729</v>
+        <v>1.52256445433273</v>
       </c>
     </row>
     <row r="42">
@@ -1955,25 +1955,25 @@
         <v>0.6940167642524774</v>
       </c>
       <c r="D42" t="n">
-        <v>0.6832990630181668</v>
+        <v>0.6832990630181667</v>
       </c>
       <c r="E42" t="n">
-        <v>0.7718670557643954</v>
+        <v>0.7718670557643953</v>
       </c>
       <c r="F42" t="n">
         <v>0.820909143453846</v>
       </c>
       <c r="G42" t="n">
-        <v>0.6094183932075998</v>
+        <v>0.6094183932075999</v>
       </c>
       <c r="H42" t="n">
         <v>0.6650781871754411</v>
       </c>
       <c r="I42" t="n">
-        <v>0.6470324990468254</v>
+        <v>0.6470324990468252</v>
       </c>
       <c r="J42" t="n">
-        <v>0.6341789753370949</v>
+        <v>0.634178975337095</v>
       </c>
       <c r="K42" t="n">
         <v>0.559370503848752</v>
@@ -1989,16 +1989,16 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>3.271319169465309</v>
+        <v>3.271319169465308</v>
       </c>
       <c r="D43" t="n">
         <v>3.433830217095334</v>
       </c>
       <c r="E43" t="n">
-        <v>4.002664376619295</v>
+        <v>4.002664376619293</v>
       </c>
       <c r="F43" t="n">
-        <v>4.52624597856052</v>
+        <v>4.526245978560519</v>
       </c>
       <c r="G43" t="n">
         <v>3.088640129149379</v>
@@ -2007,7 +2007,7 @@
         <v>3.716699797893328</v>
       </c>
       <c r="I43" t="n">
-        <v>3.723955571969352</v>
+        <v>3.723955571969351</v>
       </c>
       <c r="J43" t="n">
         <v>3.470494110571365</v>
@@ -2026,16 +2026,16 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>3.15339536631715</v>
+        <v>3.153395366317151</v>
       </c>
       <c r="D44" t="n">
-        <v>3.24453907624161</v>
+        <v>3.244539076241611</v>
       </c>
       <c r="E44" t="n">
-        <v>3.814693653470722</v>
+        <v>3.814693653470721</v>
       </c>
       <c r="F44" t="n">
-        <v>4.057736066514552</v>
+        <v>4.057736066514553</v>
       </c>
       <c r="G44" t="n">
         <v>2.924825411436502</v>
@@ -2044,10 +2044,10 @@
         <v>3.154096924213702</v>
       </c>
       <c r="I44" t="n">
-        <v>3.189680939164461</v>
+        <v>3.189680939164462</v>
       </c>
       <c r="J44" t="n">
-        <v>3.073867325889796</v>
+        <v>3.073867325889795</v>
       </c>
       <c r="K44" t="n">
         <v>2.743700199004734</v>
@@ -2103,7 +2103,7 @@
         <v>0.2235118912704913</v>
       </c>
       <c r="D46" t="n">
-        <v>0.1999953381298969</v>
+        <v>0.199995338129897</v>
       </c>
       <c r="E46" t="n">
         <v>0.2148466755169467</v>
@@ -2143,7 +2143,7 @@
         <v>0.4669895849410517</v>
       </c>
       <c r="E47" t="n">
-        <v>0.5001759049660636</v>
+        <v>0.5001759049660637</v>
       </c>
       <c r="F47" t="n">
         <v>0.529061068618113</v>
@@ -2152,13 +2152,13 @@
         <v>0.3688085027505199</v>
       </c>
       <c r="H47" t="n">
-        <v>0.4104482845537216</v>
+        <v>0.4104482845537215</v>
       </c>
       <c r="I47" t="n">
         <v>0.4241926742530287</v>
       </c>
       <c r="J47" t="n">
-        <v>0.3929886783906239</v>
+        <v>0.392988678390624</v>
       </c>
       <c r="K47" t="n">
         <v>0.3471389172107274</v>
@@ -2174,7 +2174,7 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>4.098409796816112</v>
+        <v>4.09840979681611</v>
       </c>
       <c r="D48" t="n">
         <v>3.916541896920994</v>
@@ -2211,13 +2211,13 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>3.690092830986738</v>
+        <v>3.690092830986739</v>
       </c>
       <c r="D49" t="n">
         <v>4.110496907706594</v>
       </c>
       <c r="E49" t="n">
-        <v>5.803133187846843</v>
+        <v>5.803133187846842</v>
       </c>
       <c r="F49" t="n">
         <v>6.616432763188414</v>
@@ -2251,7 +2251,7 @@
         <v>0.9053514842338998</v>
       </c>
       <c r="D50" t="n">
-        <v>0.9811294072972481</v>
+        <v>0.9811294072972483</v>
       </c>
       <c r="E50" t="n">
         <v>1.315098957217773</v>
@@ -2266,10 +2266,10 @@
         <v>1.416796095217368</v>
       </c>
       <c r="I50" t="n">
-        <v>1.39283982694515</v>
+        <v>1.392839826945151</v>
       </c>
       <c r="J50" t="n">
-        <v>1.431802823886493</v>
+        <v>1.431802823886492</v>
       </c>
       <c r="K50" t="n">
         <v>1.394297372093712</v>
@@ -2288,19 +2288,19 @@
         <v>34.94811920890896</v>
       </c>
       <c r="D51" t="n">
-        <v>37.64175437345483</v>
+        <v>37.64175437345484</v>
       </c>
       <c r="E51" t="n">
-        <v>48.70428133518993</v>
+        <v>48.70428133518995</v>
       </c>
       <c r="F51" t="n">
-        <v>57.85069450082749</v>
+        <v>57.85069450082747</v>
       </c>
       <c r="G51" t="n">
-        <v>46.59411389003178</v>
+        <v>46.5941138900318</v>
       </c>
       <c r="H51" t="n">
-        <v>56.90122818647084</v>
+        <v>56.90122818647082</v>
       </c>
       <c r="I51" t="n">
         <v>60.74620733180921</v>
@@ -2309,7 +2309,7 @@
         <v>68.5584954257279</v>
       </c>
       <c r="K51" t="n">
-        <v>65.59401471808684</v>
+        <v>65.59401471808685</v>
       </c>
     </row>
     <row r="52">
@@ -2322,7 +2322,7 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>0.8323732848465478</v>
+        <v>0.832373284846548</v>
       </c>
       <c r="D52" t="n">
         <v>1.100513775737837</v>
@@ -2334,7 +2334,7 @@
         <v>1.230530076484721</v>
       </c>
       <c r="G52" t="n">
-        <v>0.8769389606001275</v>
+        <v>0.8769389606001277</v>
       </c>
       <c r="H52" t="n">
         <v>1.247105766716611</v>
@@ -2343,7 +2343,7 @@
         <v>1.006388170668858</v>
       </c>
       <c r="J52" t="n">
-        <v>0.9981374978314596</v>
+        <v>0.9981374978314594</v>
       </c>
       <c r="K52" t="n">
         <v>0.7859846068301354</v>
@@ -2402,22 +2402,22 @@
         <v>42.389419138661</v>
       </c>
       <c r="E54" t="n">
-        <v>37.52226872580191</v>
+        <v>37.5222687258019</v>
       </c>
       <c r="F54" t="n">
         <v>35.49881686769807</v>
       </c>
       <c r="G54" t="n">
-        <v>20.04104485162681</v>
+        <v>20.0410448516268</v>
       </c>
       <c r="H54" t="n">
-        <v>21.04978019439217</v>
+        <v>21.04978019439216</v>
       </c>
       <c r="I54" t="n">
         <v>21.93284819899563</v>
       </c>
       <c r="J54" t="n">
-        <v>23.89149457921598</v>
+        <v>23.89149457921599</v>
       </c>
       <c r="K54" t="n">
         <v>23.16309936597185</v>
@@ -2445,19 +2445,19 @@
         <v>11.52223976221918</v>
       </c>
       <c r="G55" t="n">
-        <v>8.111383077145341</v>
+        <v>8.111383077145343</v>
       </c>
       <c r="H55" t="n">
         <v>8.612189240653395</v>
       </c>
       <c r="I55" t="n">
-        <v>8.83093833250412</v>
+        <v>8.830938332504118</v>
       </c>
       <c r="J55" t="n">
         <v>8.512402720388465</v>
       </c>
       <c r="K55" t="n">
-        <v>7.528094925503791</v>
+        <v>7.52809492550379</v>
       </c>
     </row>
     <row r="56">
@@ -2470,7 +2470,7 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>8.869260395165183</v>
+        <v>8.869260395165188</v>
       </c>
       <c r="D56" t="n">
         <v>9.72722116301683</v>
@@ -2479,7 +2479,7 @@
         <v>12.42646414168459</v>
       </c>
       <c r="F56" t="n">
-        <v>14.5142298337049</v>
+        <v>14.51422983370489</v>
       </c>
       <c r="G56" t="n">
         <v>12.013478911605</v>
@@ -2494,7 +2494,7 @@
         <v>15.96111833250371</v>
       </c>
       <c r="K56" t="n">
-        <v>13.11432219826744</v>
+        <v>13.11432219826745</v>
       </c>
     </row>
     <row r="57">
@@ -2516,19 +2516,19 @@
         <v>2.133536830281491</v>
       </c>
       <c r="F57" t="n">
-        <v>2.430851938853152</v>
+        <v>2.430851938853151</v>
       </c>
       <c r="G57" t="n">
         <v>1.878250066443579</v>
       </c>
       <c r="H57" t="n">
-        <v>2.046549915438183</v>
+        <v>2.046549915438182</v>
       </c>
       <c r="I57" t="n">
-        <v>1.969484481161808</v>
+        <v>1.969484481161809</v>
       </c>
       <c r="J57" t="n">
-        <v>1.895931583128844</v>
+        <v>1.895931583128843</v>
       </c>
       <c r="K57" t="n">
         <v>1.637479044274571</v>
@@ -2544,7 +2544,7 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>0.6576327702933972</v>
+        <v>0.6576327702933971</v>
       </c>
       <c r="D58" t="n">
         <v>0.6871461180050565</v>
@@ -2553,13 +2553,13 @@
         <v>0.7284287685289127</v>
       </c>
       <c r="F58" t="n">
-        <v>0.8005391215079164</v>
+        <v>0.8005391215079165</v>
       </c>
       <c r="G58" t="n">
         <v>0.5419209647119361</v>
       </c>
       <c r="H58" t="n">
-        <v>0.6167309603895577</v>
+        <v>0.6167309603895575</v>
       </c>
       <c r="I58" t="n">
         <v>0.6507069410372859</v>
@@ -2584,7 +2584,7 @@
         <v>1.552195527017637</v>
       </c>
       <c r="D59" t="n">
-        <v>1.478328900754961</v>
+        <v>1.478328900754962</v>
       </c>
       <c r="E59" t="n">
         <v>1.563920310036504</v>
@@ -2602,7 +2602,7 @@
         <v>1.766211189293363</v>
       </c>
       <c r="J59" t="n">
-        <v>1.643628704749202</v>
+        <v>1.643628704749203</v>
       </c>
       <c r="K59" t="n">
         <v>1.371249319689213</v>
@@ -2618,10 +2618,10 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>6.504238798943928</v>
+        <v>6.504238798943927</v>
       </c>
       <c r="D60" t="n">
-        <v>7.73270421289959</v>
+        <v>7.732704212899589</v>
       </c>
       <c r="E60" t="n">
         <v>9.518830507845987</v>
@@ -2633,13 +2633,13 @@
         <v>6.912409406396918</v>
       </c>
       <c r="H60" t="n">
-        <v>7.387284032678812</v>
+        <v>7.387284032678811</v>
       </c>
       <c r="I60" t="n">
         <v>7.912664693907791</v>
       </c>
       <c r="J60" t="n">
-        <v>9.431441230658001</v>
+        <v>9.431441230658002</v>
       </c>
       <c r="K60" t="n">
         <v>8.969466857089911</v>
@@ -2655,10 +2655,10 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>0.8062850840517213</v>
+        <v>0.8062850840517212</v>
       </c>
       <c r="D61" t="n">
-        <v>0.8514945049326763</v>
+        <v>0.8514945049326762</v>
       </c>
       <c r="E61" t="n">
         <v>0.894437752327932</v>
@@ -2667,16 +2667,16 @@
         <v>0.9192689491312732</v>
       </c>
       <c r="G61" t="n">
-        <v>0.6748058001595967</v>
+        <v>0.6748058001595968</v>
       </c>
       <c r="H61" t="n">
         <v>0.7376466898840391</v>
       </c>
       <c r="I61" t="n">
-        <v>0.7074690533036009</v>
+        <v>0.7074690533036008</v>
       </c>
       <c r="J61" t="n">
-        <v>0.6632483396807517</v>
+        <v>0.6632483396807516</v>
       </c>
       <c r="K61" t="n">
         <v>0.5492267277353108</v>
@@ -2729,25 +2729,25 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>13.64027893314561</v>
+        <v>13.64027893314562</v>
       </c>
       <c r="D63" t="n">
         <v>12.28069390300469</v>
       </c>
       <c r="E63" t="n">
-        <v>10.25416433187821</v>
+        <v>10.2541643318782</v>
       </c>
       <c r="F63" t="n">
-        <v>9.60426897488426</v>
+        <v>9.604268974884254</v>
       </c>
       <c r="G63" t="n">
         <v>5.828463383350039</v>
       </c>
       <c r="H63" t="n">
-        <v>5.822995613357981</v>
+        <v>5.822995613357984</v>
       </c>
       <c r="I63" t="n">
-        <v>5.75841956273183</v>
+        <v>5.758419562731828</v>
       </c>
       <c r="J63" t="n">
         <v>5.891580462895742</v>
@@ -2812,19 +2812,19 @@
         <v>71.27849147811969</v>
       </c>
       <c r="F65" t="n">
-        <v>78.3734431740436</v>
+        <v>78.37344317404362</v>
       </c>
       <c r="G65" t="n">
-        <v>60.92854657427347</v>
+        <v>60.92854657427348</v>
       </c>
       <c r="H65" t="n">
-        <v>70.98759415940251</v>
+        <v>70.98759415940249</v>
       </c>
       <c r="I65" t="n">
         <v>63.45634324529544</v>
       </c>
       <c r="J65" t="n">
-        <v>54.23214741794909</v>
+        <v>54.23214741794911</v>
       </c>
       <c r="K65" t="n">
         <v>42.461941348627</v>
@@ -2861,10 +2861,10 @@
         <v>1.620504261535418</v>
       </c>
       <c r="J66" t="n">
-        <v>1.613412693136347</v>
+        <v>1.613412693136348</v>
       </c>
       <c r="K66" t="n">
-        <v>1.472081173013345</v>
+        <v>1.472081173013346</v>
       </c>
     </row>
     <row r="67">
@@ -2920,10 +2920,10 @@
         <v>0.6297775814879853</v>
       </c>
       <c r="E68" t="n">
-        <v>0.564692187285128</v>
+        <v>0.5646921872851279</v>
       </c>
       <c r="F68" t="n">
-        <v>0.7888408406496351</v>
+        <v>0.7888408406496353</v>
       </c>
       <c r="G68" t="n">
         <v>0.520359428223514</v>
@@ -2938,7 +2938,7 @@
         <v>0.5304326204981997</v>
       </c>
       <c r="K68" t="n">
-        <v>0.6130540361763839</v>
+        <v>0.6130540361763838</v>
       </c>
     </row>
     <row r="69">
@@ -3031,7 +3031,7 @@
         <v>17.17341077680886</v>
       </c>
       <c r="E71" t="n">
-        <v>17.14594668814286</v>
+        <v>17.14594668814285</v>
       </c>
       <c r="F71" t="n">
         <v>16.69438854711138</v>
@@ -3046,7 +3046,7 @@
         <v>9.483993890333338</v>
       </c>
       <c r="J71" t="n">
-        <v>10.38016696033819</v>
+        <v>10.3801669603382</v>
       </c>
       <c r="K71" t="n">
         <v>9.189688062153643</v>
@@ -3074,10 +3074,10 @@
         <v>6.722151136125037</v>
       </c>
       <c r="G72" t="n">
-        <v>5.888765302846094</v>
+        <v>5.888765302846093</v>
       </c>
       <c r="H72" t="n">
-        <v>7.320314629106069</v>
+        <v>7.32031462910607</v>
       </c>
       <c r="I72" t="n">
         <v>8.309978010376573</v>
@@ -3105,7 +3105,7 @@
         <v>10.00160186091533</v>
       </c>
       <c r="E73" t="n">
-        <v>9.9124959774042</v>
+        <v>9.912495977404198</v>
       </c>
       <c r="F73" t="n">
         <v>9.970119555864446</v>
@@ -3114,16 +3114,16 @@
         <v>7.122884275335439</v>
       </c>
       <c r="H73" t="n">
-        <v>7.271549336320344</v>
+        <v>7.271549336320342</v>
       </c>
       <c r="I73" t="n">
         <v>7.160790067193332</v>
       </c>
       <c r="J73" t="n">
-        <v>5.433281836922994</v>
+        <v>5.433281836922995</v>
       </c>
       <c r="K73" t="n">
-        <v>4.226124220991632</v>
+        <v>4.22612422099163</v>
       </c>
     </row>
     <row r="74">
@@ -3139,13 +3139,13 @@
         <v>5.125555264142996</v>
       </c>
       <c r="D74" t="n">
-        <v>5.182536142997731</v>
+        <v>5.18253614299773</v>
       </c>
       <c r="E74" t="n">
         <v>5.955970908905272</v>
       </c>
       <c r="F74" t="n">
-        <v>6.588457945188341</v>
+        <v>6.58845794518834</v>
       </c>
       <c r="G74" t="n">
         <v>4.806359159099508</v>
@@ -3188,10 +3188,10 @@
         <v>0.09768466762706345</v>
       </c>
       <c r="H75" t="n">
-        <v>0.1054229201425692</v>
+        <v>0.1054229201425693</v>
       </c>
       <c r="I75" t="n">
-        <v>0.09051660320343852</v>
+        <v>0.0905166032034385</v>
       </c>
       <c r="J75" t="n">
         <v>0.07720457634585302</v>
@@ -3359,7 +3359,7 @@
         <v>0.4403873389516838</v>
       </c>
       <c r="D80" t="n">
-        <v>0.5172060039158781</v>
+        <v>0.5172060039158782</v>
       </c>
       <c r="E80" t="n">
         <v>0.6311332849984369</v>
@@ -3371,7 +3371,7 @@
         <v>0.5140536940890881</v>
       </c>
       <c r="H80" t="n">
-        <v>0.5586647580872882</v>
+        <v>0.5586647580872881</v>
       </c>
       <c r="I80" t="n">
         <v>0.5500704333819083</v>
@@ -3396,10 +3396,10 @@
         <v>0.1212614168486125</v>
       </c>
       <c r="D81" t="n">
-        <v>0.09503390645514619</v>
+        <v>0.09503390645514621</v>
       </c>
       <c r="E81" t="n">
-        <v>0.08736722860797945</v>
+        <v>0.08736722860797942</v>
       </c>
       <c r="F81" t="n">
         <v>0.1043573250123749</v>
@@ -3417,7 +3417,7 @@
         <v>0.1138159282263796</v>
       </c>
       <c r="K81" t="n">
-        <v>0.09602140425518105</v>
+        <v>0.09602140425518103</v>
       </c>
     </row>
     <row r="82">
@@ -3467,7 +3467,7 @@
         </is>
       </c>
       <c r="C83" t="n">
-        <v>3.55006379738158</v>
+        <v>3.550063797381581</v>
       </c>
       <c r="D83" t="n">
         <v>3.562794894653635</v>
@@ -3488,7 +3488,7 @@
         <v>4.547162423759946</v>
       </c>
       <c r="J83" t="n">
-        <v>5.295652822652454</v>
+        <v>5.295652822652453</v>
       </c>
       <c r="K83" t="n">
         <v>5.079524485052684</v>
@@ -3572,13 +3572,13 @@
         </is>
       </c>
       <c r="C86" t="n">
-        <v>0.990470126506192</v>
+        <v>0.9904701265061919</v>
       </c>
       <c r="D86" t="n">
         <v>0.9785126179402184</v>
       </c>
       <c r="E86" t="n">
-        <v>1.251815151376142</v>
+        <v>1.251815151376143</v>
       </c>
       <c r="F86" t="n">
         <v>1.377142705928078</v>
@@ -3661,7 +3661,7 @@
         <v>1.556682829466048</v>
       </c>
       <c r="H88" t="n">
-        <v>1.242062423127416</v>
+        <v>1.242062423127415</v>
       </c>
       <c r="I88" t="n">
         <v>1.000099417756576</v>
@@ -3816,19 +3816,19 @@
         <v>5.653949255338519</v>
       </c>
       <c r="D93" t="n">
-        <v>5.765704007907136</v>
+        <v>5.765704007907137</v>
       </c>
       <c r="E93" t="n">
-        <v>6.351131769716114</v>
+        <v>6.351131769716113</v>
       </c>
       <c r="F93" t="n">
-        <v>6.637476660744314</v>
+        <v>6.637476660744315</v>
       </c>
       <c r="G93" t="n">
         <v>4.833817766403696</v>
       </c>
       <c r="H93" t="n">
-        <v>5.22818665809279</v>
+        <v>5.228186658092789</v>
       </c>
       <c r="I93" t="n">
         <v>5.005085259265531</v>
@@ -3859,10 +3859,10 @@
         <v>0.5220689926091183</v>
       </c>
       <c r="F94" t="n">
-        <v>0.5356092512145605</v>
+        <v>0.5356092512145604</v>
       </c>
       <c r="G94" t="n">
-        <v>0.3396433615447085</v>
+        <v>0.3396433615447086</v>
       </c>
       <c r="H94" t="n">
         <v>0.3292672723985983</v>
@@ -3890,13 +3890,13 @@
         <v>4.626921696900212</v>
       </c>
       <c r="D95" t="n">
-        <v>4.697328635149976</v>
+        <v>4.697328635149975</v>
       </c>
       <c r="E95" t="n">
         <v>4.365576813849676</v>
       </c>
       <c r="F95" t="n">
-        <v>4.314444268383024</v>
+        <v>4.314444268383023</v>
       </c>
       <c r="G95" t="n">
         <v>3.254160371323757</v>
@@ -3967,7 +3967,7 @@
         <v>0.2292616428450047</v>
       </c>
       <c r="E97" t="n">
-        <v>0.3061215151641603</v>
+        <v>0.3061215151641602</v>
       </c>
       <c r="F97" t="n">
         <v>0.3571782222900166</v>
@@ -3985,7 +3985,7 @@
         <v>0.4098450255145077</v>
       </c>
       <c r="K97" t="n">
-        <v>0.3443810085100922</v>
+        <v>0.3443810085100923</v>
       </c>
     </row>
     <row r="98">
@@ -3998,7 +3998,7 @@
         </is>
       </c>
       <c r="C98" t="n">
-        <v>0.6303453787452906</v>
+        <v>0.6303453787452907</v>
       </c>
       <c r="D98" t="n">
         <v>0.5951704381130059</v>
@@ -4010,19 +4010,19 @@
         <v>0.8508541468722628</v>
       </c>
       <c r="G98" t="n">
-        <v>0.6914973275170297</v>
+        <v>0.6914973275170299</v>
       </c>
       <c r="H98" t="n">
         <v>0.8275527839921856</v>
       </c>
       <c r="I98" t="n">
-        <v>0.9490566241361532</v>
+        <v>0.9490566241361533</v>
       </c>
       <c r="J98" t="n">
-        <v>0.9430097070881089</v>
+        <v>0.9430097070881088</v>
       </c>
       <c r="K98" t="n">
-        <v>0.82618208613844</v>
+        <v>0.8261820861384399</v>
       </c>
     </row>
     <row r="99">
@@ -4041,13 +4041,13 @@
         <v>0.5244974658657959</v>
       </c>
       <c r="E99" t="n">
-        <v>0.7067045613956412</v>
+        <v>0.7067045613956413</v>
       </c>
       <c r="F99" t="n">
-        <v>0.8542762685222091</v>
+        <v>0.8542762685222092</v>
       </c>
       <c r="G99" t="n">
-        <v>0.7075012250410921</v>
+        <v>0.7075012250410923</v>
       </c>
       <c r="H99" t="n">
         <v>0.8758038789907682</v>
@@ -4059,7 +4059,7 @@
         <v>0.9078914675097122</v>
       </c>
       <c r="K99" t="n">
-        <v>0.6796794565949253</v>
+        <v>0.6796794565949252</v>
       </c>
     </row>
     <row r="100">
@@ -4075,7 +4075,7 @@
         <v>0.3871935569943207</v>
       </c>
       <c r="D100" t="n">
-        <v>0.4117441432251742</v>
+        <v>0.4117441432251743</v>
       </c>
       <c r="E100" t="n">
         <v>0.5048202682532662</v>
@@ -4093,7 +4093,7 @@
         <v>0.462984453383276</v>
       </c>
       <c r="J100" t="n">
-        <v>0.4337116253645701</v>
+        <v>0.4337116253645702</v>
       </c>
       <c r="K100" t="n">
         <v>0.3768470070687726</v>
@@ -4118,7 +4118,7 @@
         <v>0.3493777316900993</v>
       </c>
       <c r="F101" t="n">
-        <v>0.403048801131223</v>
+        <v>0.4030488011312231</v>
       </c>
       <c r="G101" t="n">
         <v>0.3054602171547147</v>
@@ -4149,19 +4149,19 @@
         <v>6.861851520909918</v>
       </c>
       <c r="D102" t="n">
-        <v>6.692836337140774</v>
+        <v>6.692836337140775</v>
       </c>
       <c r="E102" t="n">
-        <v>7.082303137208333</v>
+        <v>7.082303137208334</v>
       </c>
       <c r="F102" t="n">
         <v>8.303887284358154</v>
       </c>
       <c r="G102" t="n">
-        <v>5.509981469437388</v>
+        <v>5.509981469437387</v>
       </c>
       <c r="H102" t="n">
-        <v>6.1807448838438</v>
+        <v>6.180744883843801</v>
       </c>
       <c r="I102" t="n">
         <v>6.32410990790151</v>
@@ -4192,7 +4192,7 @@
         <v>0.1088940341754949</v>
       </c>
       <c r="F103" t="n">
-        <v>0.09948234405436038</v>
+        <v>0.09948234405436036</v>
       </c>
       <c r="G103" t="n">
         <v>0.07886459014311172</v>
@@ -4220,10 +4220,10 @@
         </is>
       </c>
       <c r="C104" t="n">
-        <v>0.2891584733520745</v>
+        <v>0.2891584733520744</v>
       </c>
       <c r="D104" t="n">
-        <v>0.2958715434272077</v>
+        <v>0.2958715434272078</v>
       </c>
       <c r="E104" t="n">
         <v>0.3467038143037878</v>
@@ -4260,7 +4260,7 @@
         <v>0.8985759323875515</v>
       </c>
       <c r="D105" t="n">
-        <v>0.8800614035598957</v>
+        <v>0.8800614035598955</v>
       </c>
       <c r="E105" t="n">
         <v>1.096626360143784</v>
@@ -4275,10 +4275,10 @@
         <v>0.9628965698899389</v>
       </c>
       <c r="I105" t="n">
-        <v>0.9405136087654687</v>
+        <v>0.9405136087654689</v>
       </c>
       <c r="J105" t="n">
-        <v>0.9332775578289134</v>
+        <v>0.9332775578289136</v>
       </c>
       <c r="K105" t="n">
         <v>0.8307471972937579</v>
@@ -4294,7 +4294,7 @@
         </is>
       </c>
       <c r="C106" t="n">
-        <v>0.7768820697874156</v>
+        <v>0.7768820697874155</v>
       </c>
       <c r="D106" t="n">
         <v>0.7235425620425215</v>
@@ -4303,7 +4303,7 @@
         <v>0.7056421558379495</v>
       </c>
       <c r="F106" t="n">
-        <v>0.678811170080305</v>
+        <v>0.6788111700803049</v>
       </c>
       <c r="G106" t="n">
         <v>0.4347342909433095</v>
@@ -4312,10 +4312,10 @@
         <v>0.47540257549109</v>
       </c>
       <c r="I106" t="n">
-        <v>0.4097773935258818</v>
+        <v>0.4097773935258817</v>
       </c>
       <c r="J106" t="n">
-        <v>0.4384531445279477</v>
+        <v>0.4384531445279476</v>
       </c>
       <c r="K106" t="n">
         <v>0.3522340457429924</v>
@@ -4374,7 +4374,7 @@
         <v>2.445327199084544</v>
       </c>
       <c r="E108" t="n">
-        <v>2.755432672434777</v>
+        <v>2.755432672434775</v>
       </c>
       <c r="F108" t="n">
         <v>2.94435339957723</v>
@@ -4479,10 +4479,10 @@
         </is>
       </c>
       <c r="C111" t="n">
-        <v>9.902777899039336</v>
+        <v>9.902777899039332</v>
       </c>
       <c r="D111" t="n">
-        <v>9.704020966901711</v>
+        <v>9.704020966901709</v>
       </c>
       <c r="E111" t="n">
         <v>10.42892004850635</v>
@@ -4494,16 +4494,16 @@
         <v>7.907246408799442</v>
       </c>
       <c r="H111" t="n">
-        <v>8.321765816703484</v>
+        <v>8.321765816703483</v>
       </c>
       <c r="I111" t="n">
-        <v>7.996063572752692</v>
+        <v>7.996063572752693</v>
       </c>
       <c r="J111" t="n">
-        <v>7.593380375905378</v>
+        <v>7.593380375905377</v>
       </c>
       <c r="K111" t="n">
-        <v>6.952996397266586</v>
+        <v>6.952996397266584</v>
       </c>
     </row>
     <row r="112">
@@ -4537,7 +4537,7 @@
         <v>2.14355970338414</v>
       </c>
       <c r="J112" t="n">
-        <v>2.060749396001381</v>
+        <v>2.06074939600138</v>
       </c>
       <c r="K112" t="n">
         <v>1.778980317925945</v>
@@ -4593,16 +4593,16 @@
         <v>0.1922614090689088</v>
       </c>
       <c r="D114" t="n">
-        <v>0.1968839357787629</v>
+        <v>0.196883935778763</v>
       </c>
       <c r="E114" t="n">
-        <v>0.2610923466220377</v>
+        <v>0.2610923466220376</v>
       </c>
       <c r="F114" t="n">
         <v>0.2794729383479174</v>
       </c>
       <c r="G114" t="n">
-        <v>0.2298752418157558</v>
+        <v>0.2298752418157559</v>
       </c>
       <c r="H114" t="n">
         <v>0.2465079963871969</v>
@@ -4633,7 +4633,7 @@
         <v>1.845668033653085</v>
       </c>
       <c r="E115" t="n">
-        <v>2.189469574897573</v>
+        <v>2.189469574897574</v>
       </c>
       <c r="F115" t="n">
         <v>2.462694969206142</v>
@@ -4710,7 +4710,7 @@
         <v>0.4908617152845697</v>
       </c>
       <c r="F117" t="n">
-        <v>0.551610709052523</v>
+        <v>0.5516107090525229</v>
       </c>
       <c r="G117" t="n">
         <v>0.3953256074263649</v>
@@ -4781,25 +4781,25 @@
         <v>2.008000395915998</v>
       </c>
       <c r="E119" t="n">
-        <v>2.79962063307671</v>
+        <v>2.799620633076709</v>
       </c>
       <c r="F119" t="n">
         <v>3.108535961016929</v>
       </c>
       <c r="G119" t="n">
-        <v>2.30897839454547</v>
+        <v>2.308978394545471</v>
       </c>
       <c r="H119" t="n">
-        <v>2.408200611654947</v>
+        <v>2.408200611654946</v>
       </c>
       <c r="I119" t="n">
         <v>2.736654604545234</v>
       </c>
       <c r="J119" t="n">
-        <v>2.238621413590939</v>
+        <v>2.238621413590938</v>
       </c>
       <c r="K119" t="n">
-        <v>2.038626247620959</v>
+        <v>2.03862624762096</v>
       </c>
     </row>
     <row r="120">
@@ -4812,10 +4812,10 @@
         </is>
       </c>
       <c r="C120" t="n">
-        <v>89.3890652789926</v>
+        <v>89.38906527899262</v>
       </c>
       <c r="D120" t="n">
-        <v>97.3614091196098</v>
+        <v>97.36140911960989</v>
       </c>
       <c r="E120" t="n">
         <v>128.2438708283648</v>
@@ -4827,13 +4827,13 @@
         <v>125.369188970414</v>
       </c>
       <c r="H120" t="n">
-        <v>155.1486273771884</v>
+        <v>155.1486273771883</v>
       </c>
       <c r="I120" t="n">
         <v>164.0950656929419</v>
       </c>
       <c r="J120" t="n">
-        <v>187.4431939786129</v>
+        <v>187.4431939786127</v>
       </c>
       <c r="K120" t="n">
         <v>175.8933423309223</v>
@@ -4941,7 +4941,7 @@
         <v>2.395122777753942</v>
       </c>
       <c r="I123" t="n">
-        <v>2.381866828967015</v>
+        <v>2.381866828967014</v>
       </c>
       <c r="J123" t="n">
         <v>2.521600121795119</v>
@@ -4963,7 +4963,7 @@
         <v>0.8423508491021996</v>
       </c>
       <c r="D124" t="n">
-        <v>0.9172390534067979</v>
+        <v>0.9172390534067978</v>
       </c>
       <c r="E124" t="n">
         <v>1.278807239534514</v>
@@ -4975,7 +4975,7 @@
         <v>1.071742056474724</v>
       </c>
       <c r="H124" t="n">
-        <v>1.286607025778293</v>
+        <v>1.286607025778292</v>
       </c>
       <c r="I124" t="n">
         <v>1.168470152588177</v>
@@ -4997,10 +4997,10 @@
         </is>
       </c>
       <c r="C125" t="n">
-        <v>0.9433579996877142</v>
+        <v>0.9433579996877141</v>
       </c>
       <c r="D125" t="n">
-        <v>0.9856704625500973</v>
+        <v>0.9856704625500972</v>
       </c>
       <c r="E125" t="n">
         <v>0.9225458288330838</v>
@@ -5040,7 +5040,7 @@
         <v>0.4339045217407702</v>
       </c>
       <c r="E126" t="n">
-        <v>0.5128915851297823</v>
+        <v>0.5128915851297822</v>
       </c>
       <c r="F126" t="n">
         <v>0.5877423660533346</v>
@@ -5049,7 +5049,7 @@
         <v>0.4639527763743559</v>
       </c>
       <c r="H126" t="n">
-        <v>0.5506956149753456</v>
+        <v>0.5506956149753455</v>
       </c>
       <c r="I126" t="n">
         <v>0.5783104384767976</v>
@@ -5058,7 +5058,7 @@
         <v>0.6713624133487146</v>
       </c>
       <c r="K126" t="n">
-        <v>0.6265600826280947</v>
+        <v>0.6265600826280946</v>
       </c>
     </row>
     <row r="127">
@@ -5145,7 +5145,7 @@
         </is>
       </c>
       <c r="C129" t="n">
-        <v>0.4367129138243286</v>
+        <v>0.4367129138243287</v>
       </c>
       <c r="D129" t="n">
         <v>0.4062652947499993</v>
@@ -5157,7 +5157,7 @@
         <v>0.5054751341144355</v>
       </c>
       <c r="G129" t="n">
-        <v>0.3672573553141594</v>
+        <v>0.3672573553141595</v>
       </c>
       <c r="H129" t="n">
         <v>0.4323753398335847</v>
@@ -5182,7 +5182,7 @@
         </is>
       </c>
       <c r="C130" t="n">
-        <v>1.008392044302398</v>
+        <v>1.008392044302397</v>
       </c>
       <c r="D130" t="n">
         <v>0.8622331856764005</v>
@@ -5194,19 +5194,19 @@
         <v>0.9084701006418925</v>
       </c>
       <c r="G130" t="n">
-        <v>0.7440301846827241</v>
+        <v>0.744030184682724</v>
       </c>
       <c r="H130" t="n">
-        <v>0.8399977773028524</v>
+        <v>0.8399977773028525</v>
       </c>
       <c r="I130" t="n">
-        <v>0.8492280955332051</v>
+        <v>0.849228095533205</v>
       </c>
       <c r="J130" t="n">
         <v>0.8491151929663158</v>
       </c>
       <c r="K130" t="n">
-        <v>0.7489448019917141</v>
+        <v>0.7489448019917142</v>
       </c>
     </row>
     <row r="131">
@@ -5234,13 +5234,13 @@
         <v>0.3542738998223628</v>
       </c>
       <c r="H131" t="n">
-        <v>0.4232595502262038</v>
+        <v>0.4232595502262039</v>
       </c>
       <c r="I131" t="n">
         <v>0.418176792821408</v>
       </c>
       <c r="J131" t="n">
-        <v>0.4002709743976233</v>
+        <v>0.4002709743976232</v>
       </c>
       <c r="K131" t="n">
         <v>0.368186149638324</v>
@@ -5302,16 +5302,16 @@
         <v>5.972547434847642</v>
       </c>
       <c r="F133" t="n">
-        <v>7.590039237502667</v>
+        <v>7.590039237502668</v>
       </c>
       <c r="G133" t="n">
-        <v>6.432496351518187</v>
+        <v>6.432496351518188</v>
       </c>
       <c r="H133" t="n">
         <v>8.078982623891376</v>
       </c>
       <c r="I133" t="n">
-        <v>9.070515937288526</v>
+        <v>9.070515937288528</v>
       </c>
       <c r="J133" t="n">
         <v>10.88132848802381</v>
@@ -5514,7 +5514,7 @@
         <v>0.06491720866364382</v>
       </c>
       <c r="H139" t="n">
-        <v>0.07801207720058879</v>
+        <v>0.07801207720058881</v>
       </c>
       <c r="I139" t="n">
         <v>0.0807098682329699</v>
@@ -5523,7 +5523,7 @@
         <v>0.04739221489579094</v>
       </c>
       <c r="K139" t="n">
-        <v>0.08247447506803254</v>
+        <v>0.08247447506803253</v>
       </c>
     </row>
     <row r="140">
